--- a/daybook-generated-files/4.xlsx
+++ b/daybook-generated-files/4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.37.221.58\file\HV\Capital DayBook\11. NOV\XLSX File\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.37.221.58\Shared Files\HV\Capital DayBook\2026\01. JAN\XLSX File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5175E329-3BDF-4906-8C9F-508BA84C41C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5CE3340-36CD-4E39-8AEC-C5FA63AFB417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="11490" xr2:uid="{D60EC564-5223-41AE-92B8-CDF76CB47E68}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="11490" xr2:uid="{82274E63-7A88-48C1-91FC-54601BC3D578}"/>
   </bookViews>
   <sheets>
     <sheet name="Suspense Head Report" sheetId="1" r:id="rId1"/>
@@ -20,18 +20,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="33">
   <si>
     <t>WESTERN RAILWAY</t>
   </si>
   <si>
-    <t>SUSPENSE HEAD   REPORT FROM 1/11/2025 TO 30/11/2025</t>
+    <t>SUSPENSE HEAD   REPORT FROM 1/1/2026 TO 31/1/2026</t>
+  </si>
+  <si>
+    <t>ALLOCATION : 28647703-***</t>
+  </si>
+  <si>
+    <t>SECTION</t>
+  </si>
+  <si>
+    <t>CO6 NUMBER</t>
+  </si>
+  <si>
+    <t>CO7 NUMBER</t>
+  </si>
+  <si>
+    <t>BOOK DATE</t>
+  </si>
+  <si>
+    <t>PARTY NAME</t>
+  </si>
+  <si>
+    <t>BILL DESC</t>
+  </si>
+  <si>
+    <t>DEBIT</t>
+  </si>
+  <si>
+    <t>CREDIT</t>
+  </si>
+  <si>
+    <t>SPU</t>
+  </si>
+  <si>
+    <t>CONTRACT ID</t>
+  </si>
+  <si>
+    <t>TAN NUMBER</t>
+  </si>
+  <si>
+    <t>UNIQUE_WORK_ID</t>
+  </si>
+  <si>
+    <t>X-I</t>
+  </si>
+  <si>
+    <t>08180125008189</t>
+  </si>
+  <si>
+    <t>08180125701396</t>
+  </si>
+  <si>
+    <t>13/01/2026</t>
+  </si>
+  <si>
+    <t>R J ZALA-MORVI</t>
+  </si>
+  <si>
+    <t>Rajkot Division :- Providing CCTV Room</t>
+  </si>
+  <si>
+    <t>577573.72</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>ENGINEERING</t>
+  </si>
+  <si>
+    <t>0818WC23000118 - WR/RJT/Civil/2023/0036</t>
+  </si>
+  <si>
+    <t>RKTS01812G</t>
+  </si>
+  <si>
+    <t>150064162008</t>
   </si>
   <si>
     <t>Allocation Total</t>
   </si>
   <si>
-    <t>0</t>
+    <t>577574</t>
+  </si>
+  <si>
+    <t>ALLOCATION : 28647763-***</t>
+  </si>
+  <si>
+    <t>51981.64</t>
+  </si>
+  <si>
+    <t>51982</t>
+  </si>
+  <si>
+    <t>ALLOCATION : 28647764-***</t>
   </si>
 </sst>
 </file>
@@ -84,8 +171,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -426,59 +516,357 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24DE5DD3-921E-400D-A4D7-BA325ECD9241}">
-  <dimension ref="A1:L4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB217A5C-8DF5-4084-B149-FE815A85A171}">
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
-    <col min="7" max="8" width="1.85546875" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="33.140625" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="10" max="10" width="38.5703125" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="4" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="F4" s="1" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
   </mergeCells>
